--- a/week-02/In Class Practice Files/Database Design Exercise 1.xlsx
+++ b/week-02/In Class Practice Files/Database Design Exercise 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swaid\Documents\DataAnalytics\week-02\In Class Practice Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1248A9-8C35-488B-89FE-3A880E822788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F0AB2E-E12F-4E06-8F61-6FFB149824B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DDFB45DB-115C-4EC1-8467-9EE6A5F5E208}"/>
+    <workbookView xWindow="975" yWindow="3420" windowWidth="21600" windowHeight="11295" xr2:uid="{DDFB45DB-115C-4EC1-8467-9EE6A5F5E208}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu Items" sheetId="1" r:id="rId1"/>
@@ -78,11 +78,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,330 +426,100 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{159CF618-6460-4D86-82DA-E6A2629A302B}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
